--- a/Karten/Karten.xlsx
+++ b/Karten/Karten.xlsx
@@ -522,7 +522,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Olli</t>
+          <t>Willy</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -538,7 +538,7 @@
       </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
-          <t>Eier, we need Eier</t>
+          <t>Was los, Meister?!</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tupac</t>
+          <t>Fabrice</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -584,7 +584,7 @@
       </c>
       <c r="F5" s="1" t="inlineStr">
         <is>
-          <t>Chill, Alter, es kommen auch gute Zeiten.</t>
+          <t>No Risk, no Story.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -614,7 +614,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Arnold Schwarzenegger</t>
+          <t>Tom</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -630,7 +630,7 @@
       </c>
       <c r="F6" s="1" t="inlineStr">
         <is>
-          <t>I choose  four</t>
+          <t>ham wir noch pep?</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Eric Cartman</t>
+          <t>Ugur</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -676,7 +676,7 @@
       </c>
       <c r="F7" s="1" t="inlineStr">
         <is>
-          <t>Respect My Authority!</t>
+          <t>einmal zwei döner</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hawk Tuah Girl</t>
+          <t>Carlin</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -768,7 +768,7 @@
       </c>
       <c r="F9" s="1" t="inlineStr">
         <is>
-          <t>Bee water my friend</t>
+          <t>guys, I lost my phone..</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="F10" s="1" t="inlineStr">
         <is>
-          <t>SUUUI ..your own card!!!</t>
+          <t>SUUUI ...your own card!!!</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leonardo DiCaprio </t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -952,7 +952,7 @@
       </c>
       <c r="F13" s="1" t="inlineStr">
         <is>
-          <t>Lets fuck up</t>
+          <t>alles Neuland.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="F14" s="1" t="inlineStr">
         <is>
-          <t>Let’s do some confusion.</t>
+          <t>Let's do some confusion.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mr Hankey</t>
+          <t>Murat Abi</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="F16" s="1" t="inlineStr">
         <is>
-          <t>Scheiße, shit happens.</t>
+          <t>Batterie abgeklemmt!</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Thierry Henry</t>
+          <t>Titi</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="F17" s="1" t="inlineStr">
         <is>
-          <t>Congratulations, you got me.</t>
+          <t>Cheers!</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
